--- a/dsa-doc/dsa-problems.xlsx
+++ b/dsa-doc/dsa-problems.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shubh\Projects\DSA\dsa-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC8942C-98CA-4242-AF78-AA2503BF217C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80A186C-87F0-4621-8803-A77D1CA84783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="330">
   <si>
     <t>Num</t>
   </si>
@@ -1013,6 +1014,9 @@
   </si>
   <si>
     <t>Tried but its hard</t>
+  </si>
+  <si>
+    <t>Locked</t>
   </si>
 </sst>
 </file>
@@ -1493,7 +1497,9 @@
       <c r="E2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4"/>
+      <c r="F2" s="4" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
@@ -1511,7 +1517,9 @@
       <c r="E3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="4" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
@@ -1529,7 +1537,9 @@
       <c r="E4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="4"/>
+      <c r="F4" s="4" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
@@ -1547,7 +1557,9 @@
       <c r="E5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F5" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
@@ -1565,7 +1577,9 @@
       <c r="E6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="6"/>
+      <c r="F6" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
@@ -1583,7 +1597,9 @@
       <c r="E7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="6"/>
+      <c r="F7" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
@@ -4494,7 +4510,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A56F67A8-8B9F-47F1-AE02-7D1177177A32}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -4517,6 +4533,11 @@
         <v>328</v>
       </c>
     </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>329</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/dsa-doc/dsa-problems.xlsx
+++ b/dsa-doc/dsa-problems.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shubh\Projects\DSA\dsa-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80A186C-87F0-4621-8803-A77D1CA84783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF4C5B7-4275-43BF-8B9E-6D127ACC4B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="552">
   <si>
     <t>Num</t>
   </si>
@@ -1017,13 +1018,773 @@
   </si>
   <si>
     <t>Locked</t>
+  </si>
+  <si>
+    <t>JAVA CORE + OOPs</t>
+  </si>
+  <si>
+    <t>1. What are the 4 pillars of OOPs? Explain each with real example.</t>
+  </si>
+  <si>
+    <t>2. What is the difference between Abstract class and Interface? When to use which?</t>
+  </si>
+  <si>
+    <t>3. Can an abstract class have a constructor? Can you instantiate it?</t>
+  </si>
+  <si>
+    <t>4. What is method overloading vs method overriding?</t>
+  </si>
+  <si>
+    <t>5. What is runtime polymorphism? How does Java achieve it?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">6. What is </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>==</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.equals()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">? What is </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>hashCode()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">7. Why do we override </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>equals()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>hashCode()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> together?</t>
+    </r>
+  </si>
+  <si>
+    <t>8. What is immutability? How do you make a class immutable?</t>
+  </si>
+  <si>
+    <t>9. Why is String immutable in Java?</t>
+  </si>
+  <si>
+    <t>10. What is the difference between String, StringBuilder, StringBuffer?</t>
+  </si>
+  <si>
+    <t>11. What is a static keyword — static variable, static method, static block?</t>
+  </si>
+  <si>
+    <t>12. What is final, finally, finalize?</t>
+  </si>
+  <si>
+    <t>13. What is the difference between checked and unchecked exceptions?</t>
+  </si>
+  <si>
+    <t>14. What is try-with-resources?</t>
+  </si>
+  <si>
+    <t>15. What is the difference between throw and throws?</t>
+  </si>
+  <si>
+    <t>16. What is a marker interface? Give examples.</t>
+  </si>
+  <si>
+    <t>17. What is object cloning — shallow copy vs deep copy?</t>
+  </si>
+  <si>
+    <t>18. What is the difference between stack memory and heap memory in Java?</t>
+  </si>
+  <si>
+    <t>19. What is garbage collection? How does it work in JVM?</t>
+  </si>
+  <si>
+    <t>20. What is the difference between JDK, JRE and JVM?</t>
+  </si>
+  <si>
+    <t>JAVA COLLECTIONS</t>
+  </si>
+  <si>
+    <t>21. What is the Collections hierarchy in Java? — List, Set, Map, Queue</t>
+  </si>
+  <si>
+    <t>22. How does HashMap work internally — hashing, buckets, collision?</t>
+  </si>
+  <si>
+    <t>23. What happens when two keys have the same hashCode in HashMap?</t>
+  </si>
+  <si>
+    <t>24. What is the difference between HashMap, LinkedHashMap, TreeMap?</t>
+  </si>
+  <si>
+    <t>25. What is the difference between HashMap and ConcurrentHashMap?</t>
+  </si>
+  <si>
+    <t>26. What is the difference between ArrayList and LinkedList?</t>
+  </si>
+  <si>
+    <t>27. What is the difference between ArrayList and Vector?</t>
+  </si>
+  <si>
+    <t>28. What is HashSet vs LinkedHashSet vs TreeSet?</t>
+  </si>
+  <si>
+    <t>29. What is the difference between Iterator and ListIterator?</t>
+  </si>
+  <si>
+    <t>30. What is fail-fast vs fail-safe iterator? Give examples.</t>
+  </si>
+  <si>
+    <t>31. What is the difference between Comparable and Comparator?</t>
+  </si>
+  <si>
+    <t>32. What is a PriorityQueue? How does it work?</t>
+  </si>
+  <si>
+    <t>33. What is a Deque? When do you use it?</t>
+  </si>
+  <si>
+    <t>34. What is Collections.sort() vs Arrays.sort()?</t>
+  </si>
+  <si>
+    <t>35. What is the difference between poll() and remove() in Queue?</t>
+  </si>
+  <si>
+    <t>JAVA MULTITHREADING</t>
+  </si>
+  <si>
+    <t>36. What is a thread? What is the difference between process and thread?</t>
+  </si>
+  <si>
+    <t>37. How do you create a thread — Thread class vs Runnable vs Callable?</t>
+  </si>
+  <si>
+    <t>38. What is the thread lifecycle — all states?</t>
+  </si>
+  <si>
+    <t>39. What is the difference between start() and run()?</t>
+  </si>
+  <si>
+    <t>40. What is synchronization? Why do we need it?</t>
+  </si>
+  <si>
+    <t>41. What is the difference between synchronized method and synchronized block?</t>
+  </si>
+  <si>
+    <t>42. What is a deadlock? How do you detect and avoid it?</t>
+  </si>
+  <si>
+    <t>43. What is the volatile keyword? When do you use it?</t>
+  </si>
+  <si>
+    <t>44. What is the difference between wait(), notify(), notifyAll()?</t>
+  </si>
+  <si>
+    <t>45. What is the difference between sleep() and wait()?</t>
+  </si>
+  <si>
+    <t>46. What is ExecutorService? Why use it over creating new threads?</t>
+  </si>
+  <si>
+    <t>47. What is a thread pool? What are the types in Java?</t>
+  </si>
+  <si>
+    <t>48. What is Future and Callable? How are they different from Runnable?</t>
+  </si>
+  <si>
+    <t>49. What is CompletableFuture? When do you use it?</t>
+  </si>
+  <si>
+    <t>50. What is CountDownLatch vs CyclicBarrier?</t>
+  </si>
+  <si>
+    <t>51. What is a race condition? Give an example.</t>
+  </si>
+  <si>
+    <t>52. What is ThreadLocal? When do you use it?</t>
+  </si>
+  <si>
+    <t>53. What is the difference between ReentrantLock and synchronized?</t>
+  </si>
+  <si>
+    <t>JAVA STREAMS + JAVA 8</t>
+  </si>
+  <si>
+    <t>54. What are the new features introduced in Java 8?</t>
+  </si>
+  <si>
+    <t>55. What is a lambda expression? Write one example.</t>
+  </si>
+  <si>
+    <t>56. What is a functional interface? Give 4 built-in examples.</t>
+  </si>
+  <si>
+    <t>57. What is the difference between Predicate, Function, Consumer, Supplier?</t>
+  </si>
+  <si>
+    <t>58. What is a Stream? What is the difference between Collection and Stream?</t>
+  </si>
+  <si>
+    <t>59. What is the difference between intermediate and terminal operations?</t>
+  </si>
+  <si>
+    <t>60. What is the difference between map() and flatMap()?</t>
+  </si>
+  <si>
+    <t>61. What is filter(), map(), collect(), reduce(), forEach()?</t>
+  </si>
+  <si>
+    <t>62. What is the difference between findFirst() and findAny()?</t>
+  </si>
+  <si>
+    <t>63. What is Optional? Why was it introduced? How do you use it?</t>
+  </si>
+  <si>
+    <t>64. What is method reference? Types of method references?</t>
+  </si>
+  <si>
+    <t>65. What is default method in interface? Why was it introduced?</t>
+  </si>
+  <si>
+    <t>66. What is Stream.distinct(), sorted(), limit(), skip()?</t>
+  </si>
+  <si>
+    <t>67. How do you convert a List to Map using Streams?</t>
+  </si>
+  <si>
+    <t>68. What is Collectors.groupingBy()? Write an example.</t>
+  </si>
+  <si>
+    <t>69. What is the difference between parallel stream and sequential stream?</t>
+  </si>
+  <si>
+    <t>SPRING BOOT</t>
+  </si>
+  <si>
+    <t>70. What is Spring Boot? How is it different from Spring Framework?</t>
+  </si>
+  <si>
+    <t>71. What is auto-configuration in Spring Boot?</t>
+  </si>
+  <si>
+    <t>72. What is the difference between @Component, @Service, @Repository, @Controller?</t>
+  </si>
+  <si>
+    <t>73. What is @RestController? How is it different from @Controller?</t>
+  </si>
+  <si>
+    <t>74. What is @Autowired? What are the types of dependency injection?</t>
+  </si>
+  <si>
+    <t>75. What is the difference between constructor injection and setter injection?</t>
+  </si>
+  <si>
+    <t>76. What is @Qualifier? When do you use it?</t>
+  </si>
+  <si>
+    <t>77. What is @Transactional? What happens if an exception occurs inside it?</t>
+  </si>
+  <si>
+    <t>78. What is @RequestMapping, @GetMapping, @PostMapping, @PutMapping, @DeleteMapping?</t>
+  </si>
+  <si>
+    <t>79. What is @PathVariable vs @RequestParam vs @RequestBody?</t>
+  </si>
+  <si>
+    <t>80. What is @SpringBootApplication — what annotations does it combine?</t>
+  </si>
+  <si>
+    <t>81. What is application.properties vs application.yml?</t>
+  </si>
+  <si>
+    <t>82. What is a Bean? What is the Bean lifecycle in Spring?</t>
+  </si>
+  <si>
+    <t>83. What is @Bean vs @Component?</t>
+  </si>
+  <si>
+    <t>84. What is @ControllerAdvice? How do you handle global exceptions?</t>
+  </si>
+  <si>
+    <t>85. What is ResponseEntity? When do you use it?</t>
+  </si>
+  <si>
+    <t>86. What is Spring Boot Actuator?</t>
+  </si>
+  <si>
+    <t>87. What is the difference between @Scope singleton and prototype?</t>
+  </si>
+  <si>
+    <t>88. How do you connect Spring Boot to a database?</t>
+  </si>
+  <si>
+    <t>89. What is Spring Boot starter — what does spring-boot-starter-web include?</t>
+  </si>
+  <si>
+    <t>MICROSERVICES</t>
+  </si>
+  <si>
+    <t>90. What is microservices architecture? How is it different from monolithic?</t>
+  </si>
+  <si>
+    <t>91. What are the advantages and disadvantages of microservices?</t>
+  </si>
+  <si>
+    <t>92. What is service discovery? How does Eureka work?</t>
+  </si>
+  <si>
+    <t>93. What is an API Gateway? Why do we need it?</t>
+  </si>
+  <si>
+    <t>94. What is load balancing in microservices?</t>
+  </si>
+  <si>
+    <t>95. What is the difference between synchronous and asynchronous communication?</t>
+  </si>
+  <si>
+    <t>96. What is a Circuit Breaker pattern? How does Resilience4j implement it?</t>
+  </si>
+  <si>
+    <t>97. What is Feign client? How is it different from RestTemplate?</t>
+  </si>
+  <si>
+    <t>98. What is the Saga pattern in microservices?</t>
+  </si>
+  <si>
+    <t>99. What is the difference between orchestration and choreography?</t>
+  </si>
+  <si>
+    <t>100. How do you handle distributed transactions in microservices?</t>
+  </si>
+  <si>
+    <t>101. What is inter-service communication — REST vs Kafka when to use which?</t>
+  </si>
+  <si>
+    <t>102. What is a Config Server in Spring Cloud?</t>
+  </si>
+  <si>
+    <t>103. How do you secure microservices communication?</t>
+  </si>
+  <si>
+    <t>104. What is the difference between monorepo and polyrepo in microservices?</t>
+  </si>
+  <si>
+    <t>KAFKA</t>
+  </si>
+  <si>
+    <t>105. What is Apache Kafka? What problem does it solve?</t>
+  </si>
+  <si>
+    <t>106. What is a topic, partition, offset, broker?</t>
+  </si>
+  <si>
+    <t>107. What is a producer and consumer in Kafka?</t>
+  </si>
+  <si>
+    <t>108. What is a consumer group? How does partition assignment work?</t>
+  </si>
+  <si>
+    <t>109. What is the role of ZooKeeper in Kafka?</t>
+  </si>
+  <si>
+    <t>110. What is the difference between at-most-once, at-least-once, exactly-once delivery?</t>
+  </si>
+  <si>
+    <t>111. How do you handle message failure and retry in Kafka?</t>
+  </si>
+  <si>
+    <t>112. What is the difference between Kafka and RabbitMQ?</t>
+  </si>
+  <si>
+    <t>113. What is a Kafka listener in Spring Boot — @KafkaListener?</t>
+  </si>
+  <si>
+    <t>114. What is retention period in Kafka?</t>
+  </si>
+  <si>
+    <t>115. How do you ensure message ordering in Kafka?</t>
+  </si>
+  <si>
+    <t>116. What is log compaction in Kafka?</t>
+  </si>
+  <si>
+    <t>SQL + DBMS</t>
+  </si>
+  <si>
+    <t>117. What is the difference between WHERE and HAVING?</t>
+  </si>
+  <si>
+    <t>118. What is the difference between INNER JOIN, LEFT JOIN, RIGHT JOIN, FULL JOIN?</t>
+  </si>
+  <si>
+    <t>119. What are ACID properties? Explain each.</t>
+  </si>
+  <si>
+    <t>120. What is normalization — 1NF, 2NF, 3NF? Give examples.</t>
+  </si>
+  <si>
+    <t>121. What is the difference between primary key, foreign key, unique key?</t>
+  </si>
+  <si>
+    <t>122. What is an index? When does it help and when does it hurt?</t>
+  </si>
+  <si>
+    <t>123. What is a clustered vs non-clustered index?</t>
+  </si>
+  <si>
+    <t>124. What is the difference between DELETE, TRUNCATE, DROP?</t>
+  </si>
+  <si>
+    <t>125. What is a subquery vs a JOIN — when to use which?</t>
+  </si>
+  <si>
+    <t>126. What is a view in SQL? What are its advantages?</t>
+  </si>
+  <si>
+    <t>127. What is a stored procedure vs a function?</t>
+  </si>
+  <si>
+    <t>128. What is a trigger in SQL?</t>
+  </si>
+  <si>
+    <t>129. What is transaction isolation level — READ COMMITTED, REPEATABLE READ, SERIALIZABLE?</t>
+  </si>
+  <si>
+    <t>130. Write a query — second highest salary.</t>
+  </si>
+  <si>
+    <t>131. Write a query — employees with salary greater than average.</t>
+  </si>
+  <si>
+    <t>132. Write a query — count employees per department.</t>
+  </si>
+  <si>
+    <t>133. Write a query — find duplicate records in a table.</t>
+  </si>
+  <si>
+    <t>134. What is GROUP BY vs ORDER BY?</t>
+  </si>
+  <si>
+    <t>135. What is a self join? Give an example.</t>
+  </si>
+  <si>
+    <t>DATABASE INDEXING + QUERY OPTIMIZATION</t>
+  </si>
+  <si>
+    <t>136. How does a database index work internally — B-Tree structure?</t>
+  </si>
+  <si>
+    <t>137. What is the difference between composite index and single column index?</t>
+  </si>
+  <si>
+    <t>138. What is a covering index?</t>
+  </si>
+  <si>
+    <t>139. What is EXPLAIN in SQL? How do you use it to optimize a query?</t>
+  </si>
+  <si>
+    <t>140. What is N+1 query problem? How do you solve it?</t>
+  </si>
+  <si>
+    <t>141. When should you NOT add an index?</t>
+  </si>
+  <si>
+    <t>142. What is query caching?</t>
+  </si>
+  <si>
+    <t>REDIS</t>
+  </si>
+  <si>
+    <t>143. What is Redis? What problem does it solve?</t>
+  </si>
+  <si>
+    <t>144. What are the data structures Redis supports?</t>
+  </si>
+  <si>
+    <t>145. What is cache-aside pattern vs write-through vs write-behind?</t>
+  </si>
+  <si>
+    <t>146. What is TTL in Redis?</t>
+  </si>
+  <si>
+    <t>147. What is the difference between Redis and Memcached?</t>
+  </si>
+  <si>
+    <t>148. How do you integrate Redis with Spring Boot?</t>
+  </si>
+  <si>
+    <t>149. What is Redis pub/sub?</t>
+  </si>
+  <si>
+    <t>150. What is cache invalidation? Why is it hard?</t>
+  </si>
+  <si>
+    <t>JPA + HIBERNATE</t>
+  </si>
+  <si>
+    <t>151. What is ORM? What problem does it solve?</t>
+  </si>
+  <si>
+    <t>152. What is the difference between JPA and Hibernate?</t>
+  </si>
+  <si>
+    <t>153. What is an Entity in JPA?</t>
+  </si>
+  <si>
+    <t>154. What is @OneToOne, @OneToMany, @ManyToOne, @ManyToMany?</t>
+  </si>
+  <si>
+    <t>155. What is FetchType.LAZY vs FetchType.EAGER?</t>
+  </si>
+  <si>
+    <t>156. What is the N+1 problem in Hibernate? How do you solve it?</t>
+  </si>
+  <si>
+    <t>157. What is JPQL vs native query in JPA?</t>
+  </si>
+  <si>
+    <t>158. What is @Transactional in JPA context?</t>
+  </si>
+  <si>
+    <t>159. What is first level cache vs second level cache in Hibernate?</t>
+  </si>
+  <si>
+    <t>160. What is the difference between save(), persist(), merge(), update()?</t>
+  </si>
+  <si>
+    <t>161. What is Hibernate dirty checking?</t>
+  </si>
+  <si>
+    <t>162. What is a Spring Data JPA repository — CrudRepository vs JpaRepository?</t>
+  </si>
+  <si>
+    <t>163. What is @Query annotation in Spring Data JPA?</t>
+  </si>
+  <si>
+    <t>SPRING SECURITY</t>
+  </si>
+  <si>
+    <t>164. What is Spring Security? What does it do?</t>
+  </si>
+  <si>
+    <t>165. What is authentication vs authorization?</t>
+  </si>
+  <si>
+    <t>166. What is JWT — how does it work end to end?</t>
+  </si>
+  <si>
+    <t>167. What is the difference between session-based and token-based authentication?</t>
+  </si>
+  <si>
+    <t>168. What is OAuth2? What is the flow?</t>
+  </si>
+  <si>
+    <t>169. What is @PreAuthorize and @PostAuthorize?</t>
+  </si>
+  <si>
+    <t>170. What is CSRF? How does Spring Security handle it?</t>
+  </si>
+  <si>
+    <t>171. What is a Security Filter Chain in Spring Security?</t>
+  </si>
+  <si>
+    <t>172. How do you implement role-based access control in Spring Boot?</t>
+  </si>
+  <si>
+    <t>JUNIT + MOCKITO</t>
+  </si>
+  <si>
+    <t>173. What is unit testing? Why is it important?</t>
+  </si>
+  <si>
+    <t>174. What is the difference between @Test, @BeforeEach, @AfterEach, @BeforeAll?</t>
+  </si>
+  <si>
+    <t>175. What is Mockito? What problem does it solve?</t>
+  </si>
+  <si>
+    <t>176. What is the difference between @Mock and @InjectMocks?</t>
+  </si>
+  <si>
+    <t>177. What is when().thenReturn() — how do you mock a method?</t>
+  </si>
+  <si>
+    <t>178. What is verify() in Mockito?</t>
+  </si>
+  <si>
+    <t>179. What is the difference between mock() and spy()?</t>
+  </si>
+  <si>
+    <t>180. What is @ExtendWith(MockitoExtension.class)?</t>
+  </si>
+  <si>
+    <t>181. How do you test a REST controller — MockMvc?</t>
+  </si>
+  <si>
+    <t>182. What is code coverage? What is a good coverage percentage?</t>
+  </si>
+  <si>
+    <t>DESIGN PATTERNS</t>
+  </si>
+  <si>
+    <t>183. What is Singleton pattern? Write thread-safe implementation.</t>
+  </si>
+  <si>
+    <t>184. What is Factory pattern? Give a real example.</t>
+  </si>
+  <si>
+    <t>185. What is Abstract Factory vs Factory Method?</t>
+  </si>
+  <si>
+    <t>186. What is Builder pattern? When do you use it?</t>
+  </si>
+  <si>
+    <t>187. What is Observer pattern? Give a real example.</t>
+  </si>
+  <si>
+    <t>188. What is Strategy pattern?</t>
+  </si>
+  <si>
+    <t>189. What is Decorator pattern?</t>
+  </si>
+  <si>
+    <t>190. What is Dependency Injection — is it a design pattern?</t>
+  </si>
+  <si>
+    <t>191. What is the difference between creational, structural and behavioral patterns?</t>
+  </si>
+  <si>
+    <t>192. What design patterns does Spring Framework use internally?</t>
+  </si>
+  <si>
+    <t>REACT JS + FRONTEND (last phase)</t>
+  </si>
+  <si>
+    <t>193. What is React? What problem does it solve?</t>
+  </si>
+  <si>
+    <t>194. What is the difference between class component and functional component?</t>
+  </si>
+  <si>
+    <t>195. What is JSX?</t>
+  </si>
+  <si>
+    <t>196. What is state vs props?</t>
+  </si>
+  <si>
+    <t>197. What is the component lifecycle — class based?</t>
+  </si>
+  <si>
+    <t>198. What are React Hooks — useState, useEffect, useCallback, useMemo, useRef?</t>
+  </si>
+  <si>
+    <t>199. What is the difference between useEffect with no dependency, empty array, and with dependency?</t>
+  </si>
+  <si>
+    <t>200. What is Redux? What problem does it solve?</t>
+  </si>
+  <si>
+    <t>201. What is Redux Toolkit — createSlice, createAsyncThunk?</t>
+  </si>
+  <si>
+    <t>202. What is the difference between Redux and Context API?</t>
+  </si>
+  <si>
+    <t>203. What is React Router?</t>
+  </si>
+  <si>
+    <t>204. What is lazy loading in React?</t>
+  </si>
+  <si>
+    <t>205. What is Virtual DOM? How does React reconciliation work?</t>
+  </si>
+  <si>
+    <t>206. What is Material UI? How do you use a theme?</t>
+  </si>
+  <si>
+    <t>207. What is the difference between controlled and uncontrolled components?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1069,6 +1830,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1131,7 +1905,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1168,6 +1942,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1451,7 +2231,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F151"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
     <col min="2" max="2" width="35.21875" customWidth="1"/>
@@ -1461,7 +2241,7 @@
     <col min="6" max="6" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="26.4" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1481,7 +2261,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="15" thickBot="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1501,7 +2281,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="15" thickBot="1">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1521,7 +2301,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="15" thickBot="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1541,7 +2321,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="15" thickBot="1">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -1561,7 +2341,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="15" thickBot="1">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -1581,7 +2361,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="15" thickBot="1">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -1601,7 +2381,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="15" thickBot="1">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -1617,9 +2397,11 @@
       <c r="E8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F8" s="6" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" thickBot="1">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -1635,9 +2417,11 @@
       <c r="E9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F9" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" thickBot="1">
       <c r="A10" s="6">
         <v>9</v>
       </c>
@@ -1653,9 +2437,11 @@
       <c r="E10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F10" s="6" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" thickBot="1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -1671,9 +2457,11 @@
       <c r="E11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F11" s="4" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" thickBot="1">
       <c r="A12" s="6">
         <v>11</v>
       </c>
@@ -1689,9 +2477,11 @@
       <c r="E12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F12" s="6" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" thickBot="1">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -1709,7 +2499,7 @@
       </c>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="15" thickBot="1">
       <c r="A14" s="6">
         <v>13</v>
       </c>
@@ -1727,7 +2517,7 @@
       </c>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="15" thickBot="1">
       <c r="A15" s="6">
         <v>14</v>
       </c>
@@ -1745,7 +2535,7 @@
       </c>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="15" thickBot="1">
       <c r="A16" s="6">
         <v>15</v>
       </c>
@@ -1763,7 +2553,7 @@
       </c>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="15" thickBot="1">
       <c r="A17" s="6">
         <v>16</v>
       </c>
@@ -1781,7 +2571,7 @@
       </c>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="15" thickBot="1">
       <c r="A18" s="6">
         <v>17</v>
       </c>
@@ -1799,7 +2589,7 @@
       </c>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="15" thickBot="1">
       <c r="A19" s="6">
         <v>18</v>
       </c>
@@ -1817,7 +2607,7 @@
       </c>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="15" thickBot="1">
       <c r="A20" s="9">
         <v>19</v>
       </c>
@@ -1835,7 +2625,7 @@
       </c>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="15" thickBot="1">
       <c r="A21" s="9">
         <v>20</v>
       </c>
@@ -1853,7 +2643,7 @@
       </c>
       <c r="F21" s="9"/>
     </row>
-    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="15" thickBot="1">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -1871,7 +2661,7 @@
       </c>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="15" thickBot="1">
       <c r="A23" s="6">
         <v>22</v>
       </c>
@@ -1889,7 +2679,7 @@
       </c>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="15" thickBot="1">
       <c r="A24" s="6">
         <v>23</v>
       </c>
@@ -1907,7 +2697,7 @@
       </c>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="15" thickBot="1">
       <c r="A25" s="6">
         <v>24</v>
       </c>
@@ -1925,7 +2715,7 @@
       </c>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" ht="15" thickBot="1">
       <c r="A26" s="6">
         <v>25</v>
       </c>
@@ -1943,7 +2733,7 @@
       </c>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="15" thickBot="1">
       <c r="A27" s="6">
         <v>26</v>
       </c>
@@ -1961,7 +2751,7 @@
       </c>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="15" thickBot="1">
       <c r="A28" s="9">
         <v>27</v>
       </c>
@@ -1979,7 +2769,7 @@
       </c>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" ht="15" thickBot="1">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -1997,7 +2787,7 @@
       </c>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="15" thickBot="1">
       <c r="A30" s="6">
         <v>29</v>
       </c>
@@ -2015,7 +2805,7 @@
       </c>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="15" thickBot="1">
       <c r="A31" s="6">
         <v>30</v>
       </c>
@@ -2033,7 +2823,7 @@
       </c>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="15" thickBot="1">
       <c r="A32" s="6">
         <v>31</v>
       </c>
@@ -2051,7 +2841,7 @@
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" ht="15" thickBot="1">
       <c r="A33" s="6">
         <v>32</v>
       </c>
@@ -2069,7 +2859,7 @@
       </c>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="15" thickBot="1">
       <c r="A34" s="6">
         <v>33</v>
       </c>
@@ -2087,7 +2877,7 @@
       </c>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="15" thickBot="1">
       <c r="A35" s="9">
         <v>34</v>
       </c>
@@ -2105,7 +2895,7 @@
       </c>
       <c r="F35" s="9"/>
     </row>
-    <row r="36" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="15" thickBot="1">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -2123,7 +2913,7 @@
       </c>
       <c r="F36" s="4"/>
     </row>
-    <row r="37" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="15" thickBot="1">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -2141,7 +2931,7 @@
       </c>
       <c r="F37" s="4"/>
     </row>
-    <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="15" thickBot="1">
       <c r="A38" s="6">
         <v>37</v>
       </c>
@@ -2159,7 +2949,7 @@
       </c>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" ht="15" thickBot="1">
       <c r="A39" s="6">
         <v>38</v>
       </c>
@@ -2177,7 +2967,7 @@
       </c>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" ht="15" thickBot="1">
       <c r="A40" s="6">
         <v>39</v>
       </c>
@@ -2195,7 +2985,7 @@
       </c>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" ht="15" thickBot="1">
       <c r="A41" s="6">
         <v>40</v>
       </c>
@@ -2213,7 +3003,7 @@
       </c>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" ht="15" thickBot="1">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -2231,7 +3021,7 @@
       </c>
       <c r="F42" s="4"/>
     </row>
-    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" ht="15" thickBot="1">
       <c r="A43" s="6">
         <v>42</v>
       </c>
@@ -2249,7 +3039,7 @@
       </c>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="15" thickBot="1">
       <c r="A44" s="6">
         <v>43</v>
       </c>
@@ -2267,7 +3057,7 @@
       </c>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" ht="15" thickBot="1">
       <c r="A45" s="9">
         <v>44</v>
       </c>
@@ -2285,7 +3075,7 @@
       </c>
       <c r="F45" s="9"/>
     </row>
-    <row r="46" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" ht="15" thickBot="1">
       <c r="A46" s="9">
         <v>45</v>
       </c>
@@ -2303,7 +3093,7 @@
       </c>
       <c r="F46" s="9"/>
     </row>
-    <row r="47" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" ht="15" thickBot="1">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -2321,7 +3111,7 @@
       </c>
       <c r="F47" s="4"/>
     </row>
-    <row r="48" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" ht="15" thickBot="1">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -2339,7 +3129,7 @@
       </c>
       <c r="F48" s="4"/>
     </row>
-    <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="15" thickBot="1">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -2357,7 +3147,7 @@
       </c>
       <c r="F49" s="4"/>
     </row>
-    <row r="50" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" ht="15" thickBot="1">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -2375,7 +3165,7 @@
       </c>
       <c r="F50" s="4"/>
     </row>
-    <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" ht="15" thickBot="1">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -2393,7 +3183,7 @@
       </c>
       <c r="F51" s="4"/>
     </row>
-    <row r="52" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" ht="15" thickBot="1">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -2411,7 +3201,7 @@
       </c>
       <c r="F52" s="4"/>
     </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="15" thickBot="1">
       <c r="A53" s="6">
         <v>52</v>
       </c>
@@ -2429,7 +3219,7 @@
       </c>
       <c r="F53" s="6"/>
     </row>
-    <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" ht="15" thickBot="1">
       <c r="A54" s="6">
         <v>53</v>
       </c>
@@ -2447,7 +3237,7 @@
       </c>
       <c r="F54" s="6"/>
     </row>
-    <row r="55" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" ht="15" thickBot="1">
       <c r="A55" s="6">
         <v>54</v>
       </c>
@@ -2465,7 +3255,7 @@
       </c>
       <c r="F55" s="6"/>
     </row>
-    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" ht="15" thickBot="1">
       <c r="A56" s="6">
         <v>55</v>
       </c>
@@ -2483,7 +3273,7 @@
       </c>
       <c r="F56" s="6"/>
     </row>
-    <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" ht="15" thickBot="1">
       <c r="A57" s="6">
         <v>56</v>
       </c>
@@ -2501,7 +3291,7 @@
       </c>
       <c r="F57" s="6"/>
     </row>
-    <row r="58" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" ht="15" thickBot="1">
       <c r="A58" s="6">
         <v>57</v>
       </c>
@@ -2519,7 +3309,7 @@
       </c>
       <c r="F58" s="6"/>
     </row>
-    <row r="59" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" ht="15" thickBot="1">
       <c r="A59" s="6">
         <v>58</v>
       </c>
@@ -2537,7 +3327,7 @@
       </c>
       <c r="F59" s="6"/>
     </row>
-    <row r="60" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" ht="15" thickBot="1">
       <c r="A60" s="9">
         <v>59</v>
       </c>
@@ -2555,7 +3345,7 @@
       </c>
       <c r="F60" s="9"/>
     </row>
-    <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" ht="15" thickBot="1">
       <c r="A61" s="9">
         <v>60</v>
       </c>
@@ -2573,7 +3363,7 @@
       </c>
       <c r="F61" s="9"/>
     </row>
-    <row r="62" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" ht="15" thickBot="1">
       <c r="A62" s="6">
         <v>61</v>
       </c>
@@ -2591,7 +3381,7 @@
       </c>
       <c r="F62" s="6"/>
     </row>
-    <row r="63" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" ht="15" thickBot="1">
       <c r="A63" s="6">
         <v>62</v>
       </c>
@@ -2609,7 +3399,7 @@
       </c>
       <c r="F63" s="6"/>
     </row>
-    <row r="64" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" ht="15" thickBot="1">
       <c r="A64" s="9">
         <v>63</v>
       </c>
@@ -2627,7 +3417,7 @@
       </c>
       <c r="F64" s="9"/>
     </row>
-    <row r="65" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" ht="15" thickBot="1">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -2645,7 +3435,7 @@
       </c>
       <c r="F65" s="4"/>
     </row>
-    <row r="66" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" ht="15" thickBot="1">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -2663,7 +3453,7 @@
       </c>
       <c r="F66" s="4"/>
     </row>
-    <row r="67" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" ht="15" thickBot="1">
       <c r="A67" s="6">
         <v>66</v>
       </c>
@@ -2681,7 +3471,7 @@
       </c>
       <c r="F67" s="6"/>
     </row>
-    <row r="68" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" ht="15" thickBot="1">
       <c r="A68" s="6">
         <v>67</v>
       </c>
@@ -2699,7 +3489,7 @@
       </c>
       <c r="F68" s="6"/>
     </row>
-    <row r="69" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" ht="15" thickBot="1">
       <c r="A69" s="6">
         <v>68</v>
       </c>
@@ -2717,7 +3507,7 @@
       </c>
       <c r="F69" s="6"/>
     </row>
-    <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" ht="15" thickBot="1">
       <c r="A70" s="6">
         <v>69</v>
       </c>
@@ -2735,7 +3525,7 @@
       </c>
       <c r="F70" s="6"/>
     </row>
-    <row r="71" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" ht="15" thickBot="1">
       <c r="A71" s="9">
         <v>70</v>
       </c>
@@ -2753,7 +3543,7 @@
       </c>
       <c r="F71" s="9"/>
     </row>
-    <row r="72" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" ht="15" thickBot="1">
       <c r="A72" s="6">
         <v>71</v>
       </c>
@@ -2771,7 +3561,7 @@
       </c>
       <c r="F72" s="6"/>
     </row>
-    <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="15" thickBot="1">
       <c r="A73" s="6">
         <v>72</v>
       </c>
@@ -2789,7 +3579,7 @@
       </c>
       <c r="F73" s="6"/>
     </row>
-    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" ht="15" thickBot="1">
       <c r="A74" s="6">
         <v>73</v>
       </c>
@@ -2807,7 +3597,7 @@
       </c>
       <c r="F74" s="6"/>
     </row>
-    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" ht="15" thickBot="1">
       <c r="A75" s="6">
         <v>74</v>
       </c>
@@ -2825,7 +3615,7 @@
       </c>
       <c r="F75" s="6"/>
     </row>
-    <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" ht="15" thickBot="1">
       <c r="A76" s="6">
         <v>75</v>
       </c>
@@ -2843,7 +3633,7 @@
       </c>
       <c r="F76" s="6"/>
     </row>
-    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" ht="15" thickBot="1">
       <c r="A77" s="6">
         <v>76</v>
       </c>
@@ -2861,7 +3651,7 @@
       </c>
       <c r="F77" s="6"/>
     </row>
-    <row r="78" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" ht="15" thickBot="1">
       <c r="A78" s="6">
         <v>77</v>
       </c>
@@ -2879,7 +3669,7 @@
       </c>
       <c r="F78" s="6"/>
     </row>
-    <row r="79" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" ht="15" thickBot="1">
       <c r="A79" s="6">
         <v>78</v>
       </c>
@@ -2897,7 +3687,7 @@
       </c>
       <c r="F79" s="6"/>
     </row>
-    <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" ht="15" thickBot="1">
       <c r="A80" s="9">
         <v>79</v>
       </c>
@@ -2915,7 +3705,7 @@
       </c>
       <c r="F80" s="9"/>
     </row>
-    <row r="81" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" ht="15" thickBot="1">
       <c r="A81" s="6">
         <v>80</v>
       </c>
@@ -2933,7 +3723,7 @@
       </c>
       <c r="F81" s="6"/>
     </row>
-    <row r="82" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" ht="15" thickBot="1">
       <c r="A82" s="6">
         <v>81</v>
       </c>
@@ -2951,7 +3741,7 @@
       </c>
       <c r="F82" s="6"/>
     </row>
-    <row r="83" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" ht="15" thickBot="1">
       <c r="A83" s="6">
         <v>82</v>
       </c>
@@ -2969,7 +3759,7 @@
       </c>
       <c r="F83" s="6"/>
     </row>
-    <row r="84" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" ht="15" thickBot="1">
       <c r="A84" s="6">
         <v>83</v>
       </c>
@@ -2987,7 +3777,7 @@
       </c>
       <c r="F84" s="6"/>
     </row>
-    <row r="85" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" ht="15" thickBot="1">
       <c r="A85" s="6">
         <v>84</v>
       </c>
@@ -3005,7 +3795,7 @@
       </c>
       <c r="F85" s="6"/>
     </row>
-    <row r="86" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" ht="15" thickBot="1">
       <c r="A86" s="6">
         <v>85</v>
       </c>
@@ -3023,7 +3813,7 @@
       </c>
       <c r="F86" s="6"/>
     </row>
-    <row r="87" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" ht="15" thickBot="1">
       <c r="A87" s="6">
         <v>86</v>
       </c>
@@ -3041,7 +3831,7 @@
       </c>
       <c r="F87" s="6"/>
     </row>
-    <row r="88" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" ht="15" thickBot="1">
       <c r="A88" s="6">
         <v>87</v>
       </c>
@@ -3059,7 +3849,7 @@
       </c>
       <c r="F88" s="6"/>
     </row>
-    <row r="89" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" ht="15" thickBot="1">
       <c r="A89" s="6">
         <v>88</v>
       </c>
@@ -3077,7 +3867,7 @@
       </c>
       <c r="F89" s="6"/>
     </row>
-    <row r="90" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" ht="15" thickBot="1">
       <c r="A90" s="6">
         <v>89</v>
       </c>
@@ -3095,7 +3885,7 @@
       </c>
       <c r="F90" s="6"/>
     </row>
-    <row r="91" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" ht="15" thickBot="1">
       <c r="A91" s="6">
         <v>90</v>
       </c>
@@ -3113,7 +3903,7 @@
       </c>
       <c r="F91" s="6"/>
     </row>
-    <row r="92" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" ht="15" thickBot="1">
       <c r="A92" s="6">
         <v>91</v>
       </c>
@@ -3131,7 +3921,7 @@
       </c>
       <c r="F92" s="6"/>
     </row>
-    <row r="93" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" ht="15" thickBot="1">
       <c r="A93" s="9">
         <v>92</v>
       </c>
@@ -3149,7 +3939,7 @@
       </c>
       <c r="F93" s="9"/>
     </row>
-    <row r="94" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" ht="15" thickBot="1">
       <c r="A94" s="9">
         <v>93</v>
       </c>
@@ -3167,7 +3957,7 @@
       </c>
       <c r="F94" s="9"/>
     </row>
-    <row r="95" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" ht="15" thickBot="1">
       <c r="A95" s="6">
         <v>94</v>
       </c>
@@ -3185,7 +3975,7 @@
       </c>
       <c r="F95" s="6"/>
     </row>
-    <row r="96" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" ht="15" thickBot="1">
       <c r="A96" s="6">
         <v>95</v>
       </c>
@@ -3203,7 +3993,7 @@
       </c>
       <c r="F96" s="6"/>
     </row>
-    <row r="97" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" ht="15" thickBot="1">
       <c r="A97" s="9">
         <v>96</v>
       </c>
@@ -3221,7 +4011,7 @@
       </c>
       <c r="F97" s="9"/>
     </row>
-    <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" ht="15" thickBot="1">
       <c r="A98" s="9">
         <v>97</v>
       </c>
@@ -3239,7 +4029,7 @@
       </c>
       <c r="F98" s="9"/>
     </row>
-    <row r="99" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" ht="15" thickBot="1">
       <c r="A99" s="6">
         <v>98</v>
       </c>
@@ -3257,7 +4047,7 @@
       </c>
       <c r="F99" s="6"/>
     </row>
-    <row r="100" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" ht="15" thickBot="1">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -3275,7 +4065,7 @@
       </c>
       <c r="F100" s="4"/>
     </row>
-    <row r="101" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" ht="15" thickBot="1">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -3293,7 +4083,7 @@
       </c>
       <c r="F101" s="4"/>
     </row>
-    <row r="102" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" ht="15" thickBot="1">
       <c r="A102" s="6">
         <v>101</v>
       </c>
@@ -3311,7 +4101,7 @@
       </c>
       <c r="F102" s="6"/>
     </row>
-    <row r="103" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" ht="15" thickBot="1">
       <c r="A103" s="6">
         <v>102</v>
       </c>
@@ -3329,7 +4119,7 @@
       </c>
       <c r="F103" s="6"/>
     </row>
-    <row r="104" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" ht="15" thickBot="1">
       <c r="A104" s="6">
         <v>103</v>
       </c>
@@ -3347,7 +4137,7 @@
       </c>
       <c r="F104" s="6"/>
     </row>
-    <row r="105" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" ht="15" thickBot="1">
       <c r="A105" s="6">
         <v>104</v>
       </c>
@@ -3365,7 +4155,7 @@
       </c>
       <c r="F105" s="6"/>
     </row>
-    <row r="106" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" ht="15" thickBot="1">
       <c r="A106" s="6">
         <v>105</v>
       </c>
@@ -3383,7 +4173,7 @@
       </c>
       <c r="F106" s="6"/>
     </row>
-    <row r="107" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" ht="15" thickBot="1">
       <c r="A107" s="6">
         <v>106</v>
       </c>
@@ -3401,7 +4191,7 @@
       </c>
       <c r="F107" s="6"/>
     </row>
-    <row r="108" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" ht="15" thickBot="1">
       <c r="A108" s="6">
         <v>107</v>
       </c>
@@ -3419,7 +4209,7 @@
       </c>
       <c r="F108" s="6"/>
     </row>
-    <row r="109" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" ht="15" thickBot="1">
       <c r="A109" s="6">
         <v>108</v>
       </c>
@@ -3437,7 +4227,7 @@
       </c>
       <c r="F109" s="6"/>
     </row>
-    <row r="110" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" ht="15" thickBot="1">
       <c r="A110" s="6">
         <v>109</v>
       </c>
@@ -3455,7 +4245,7 @@
       </c>
       <c r="F110" s="6"/>
     </row>
-    <row r="111" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" ht="15" thickBot="1">
       <c r="A111" s="6">
         <v>110</v>
       </c>
@@ -3473,7 +4263,7 @@
       </c>
       <c r="F111" s="6"/>
     </row>
-    <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" ht="15" thickBot="1">
       <c r="A112" s="6">
         <v>111</v>
       </c>
@@ -3491,7 +4281,7 @@
       </c>
       <c r="F112" s="6"/>
     </row>
-    <row r="113" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" ht="15" thickBot="1">
       <c r="A113" s="6">
         <v>112</v>
       </c>
@@ -3509,7 +4299,7 @@
       </c>
       <c r="F113" s="6"/>
     </row>
-    <row r="114" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" ht="15" thickBot="1">
       <c r="A114" s="6">
         <v>113</v>
       </c>
@@ -3527,7 +4317,7 @@
       </c>
       <c r="F114" s="6"/>
     </row>
-    <row r="115" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" ht="15" thickBot="1">
       <c r="A115" s="6">
         <v>114</v>
       </c>
@@ -3545,7 +4335,7 @@
       </c>
       <c r="F115" s="6"/>
     </row>
-    <row r="116" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" ht="15" thickBot="1">
       <c r="A116" s="6">
         <v>115</v>
       </c>
@@ -3563,7 +4353,7 @@
       </c>
       <c r="F116" s="6"/>
     </row>
-    <row r="117" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" ht="15" thickBot="1">
       <c r="A117" s="6">
         <v>116</v>
       </c>
@@ -3581,7 +4371,7 @@
       </c>
       <c r="F117" s="6"/>
     </row>
-    <row r="118" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" ht="15" thickBot="1">
       <c r="A118" s="9">
         <v>117</v>
       </c>
@@ -3599,7 +4389,7 @@
       </c>
       <c r="F118" s="9"/>
     </row>
-    <row r="119" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" ht="15" thickBot="1">
       <c r="A119" s="9">
         <v>118</v>
       </c>
@@ -3617,7 +4407,7 @@
       </c>
       <c r="F119" s="9"/>
     </row>
-    <row r="120" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" ht="15" thickBot="1">
       <c r="A120" s="6">
         <v>119</v>
       </c>
@@ -3635,7 +4425,7 @@
       </c>
       <c r="F120" s="6"/>
     </row>
-    <row r="121" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" ht="15" thickBot="1">
       <c r="A121" s="9">
         <v>120</v>
       </c>
@@ -3653,7 +4443,7 @@
       </c>
       <c r="F121" s="9"/>
     </row>
-    <row r="122" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" ht="15" thickBot="1">
       <c r="A122" s="9">
         <v>121</v>
       </c>
@@ -3671,7 +4461,7 @@
       </c>
       <c r="F122" s="9"/>
     </row>
-    <row r="123" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" ht="15" thickBot="1">
       <c r="A123" s="6">
         <v>122</v>
       </c>
@@ -3689,7 +4479,7 @@
       </c>
       <c r="F123" s="6"/>
     </row>
-    <row r="124" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" ht="15" thickBot="1">
       <c r="A124" s="6">
         <v>123</v>
       </c>
@@ -3707,7 +4497,7 @@
       </c>
       <c r="F124" s="6"/>
     </row>
-    <row r="125" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" ht="15" thickBot="1">
       <c r="A125" s="6">
         <v>124</v>
       </c>
@@ -3725,7 +4515,7 @@
       </c>
       <c r="F125" s="6"/>
     </row>
-    <row r="126" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" ht="15" thickBot="1">
       <c r="A126" s="6">
         <v>125</v>
       </c>
@@ -3743,7 +4533,7 @@
       </c>
       <c r="F126" s="6"/>
     </row>
-    <row r="127" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" ht="15" thickBot="1">
       <c r="A127" s="6">
         <v>126</v>
       </c>
@@ -3761,7 +4551,7 @@
       </c>
       <c r="F127" s="6"/>
     </row>
-    <row r="128" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" ht="15" thickBot="1">
       <c r="A128" s="6">
         <v>127</v>
       </c>
@@ -3779,7 +4569,7 @@
       </c>
       <c r="F128" s="6"/>
     </row>
-    <row r="129" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" ht="15" thickBot="1">
       <c r="A129" s="6">
         <v>128</v>
       </c>
@@ -3797,7 +4587,7 @@
       </c>
       <c r="F129" s="6"/>
     </row>
-    <row r="130" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" ht="15" thickBot="1">
       <c r="A130" s="6">
         <v>129</v>
       </c>
@@ -3815,7 +4605,7 @@
       </c>
       <c r="F130" s="6"/>
     </row>
-    <row r="131" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" ht="15" thickBot="1">
       <c r="A131" s="6">
         <v>130</v>
       </c>
@@ -3833,7 +4623,7 @@
       </c>
       <c r="F131" s="6"/>
     </row>
-    <row r="132" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" ht="15" thickBot="1">
       <c r="A132" s="6">
         <v>131</v>
       </c>
@@ -3851,7 +4641,7 @@
       </c>
       <c r="F132" s="6"/>
     </row>
-    <row r="133" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6" ht="15" thickBot="1">
       <c r="A133" s="6">
         <v>132</v>
       </c>
@@ -3869,7 +4659,7 @@
       </c>
       <c r="F133" s="6"/>
     </row>
-    <row r="134" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" ht="15" thickBot="1">
       <c r="A134" s="4">
         <v>133</v>
       </c>
@@ -3887,7 +4677,7 @@
       </c>
       <c r="F134" s="4"/>
     </row>
-    <row r="135" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" ht="15" thickBot="1">
       <c r="A135" s="6">
         <v>134</v>
       </c>
@@ -3905,7 +4695,7 @@
       </c>
       <c r="F135" s="6"/>
     </row>
-    <row r="136" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" ht="15" thickBot="1">
       <c r="A136" s="9">
         <v>135</v>
       </c>
@@ -3923,7 +4713,7 @@
       </c>
       <c r="F136" s="9"/>
     </row>
-    <row r="137" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" ht="15" thickBot="1">
       <c r="A137" s="6">
         <v>136</v>
       </c>
@@ -3941,7 +4731,7 @@
       </c>
       <c r="F137" s="6"/>
     </row>
-    <row r="138" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" ht="15" thickBot="1">
       <c r="A138" s="6">
         <v>137</v>
       </c>
@@ -3959,7 +4749,7 @@
       </c>
       <c r="F138" s="6"/>
     </row>
-    <row r="139" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" ht="15" thickBot="1">
       <c r="A139" s="6">
         <v>138</v>
       </c>
@@ -3977,7 +4767,7 @@
       </c>
       <c r="F139" s="6"/>
     </row>
-    <row r="140" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" ht="15" thickBot="1">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -3995,7 +4785,7 @@
       </c>
       <c r="F140" s="4"/>
     </row>
-    <row r="141" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" ht="15" thickBot="1">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -4013,7 +4803,7 @@
       </c>
       <c r="F141" s="4"/>
     </row>
-    <row r="142" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" ht="15" thickBot="1">
       <c r="A142" s="6">
         <v>141</v>
       </c>
@@ -4031,7 +4821,7 @@
       </c>
       <c r="F142" s="6"/>
     </row>
-    <row r="143" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" ht="15" thickBot="1">
       <c r="A143" s="6">
         <v>142</v>
       </c>
@@ -4049,7 +4839,7 @@
       </c>
       <c r="F143" s="6"/>
     </row>
-    <row r="144" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" ht="15" thickBot="1">
       <c r="A144" s="6">
         <v>143</v>
       </c>
@@ -4067,7 +4857,7 @@
       </c>
       <c r="F144" s="6"/>
     </row>
-    <row r="145" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" ht="15" thickBot="1">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -4085,7 +4875,7 @@
       </c>
       <c r="F145" s="4"/>
     </row>
-    <row r="146" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" ht="15" thickBot="1">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -4103,7 +4893,7 @@
       </c>
       <c r="F146" s="4"/>
     </row>
-    <row r="147" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" ht="15" thickBot="1">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -4121,7 +4911,7 @@
       </c>
       <c r="F147" s="4"/>
     </row>
-    <row r="148" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" ht="15" thickBot="1">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -4139,7 +4929,7 @@
       </c>
       <c r="F148" s="4"/>
     </row>
-    <row r="149" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" ht="15" thickBot="1">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -4157,7 +4947,7 @@
       </c>
       <c r="F149" s="4"/>
     </row>
-    <row r="150" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" ht="15" thickBot="1">
       <c r="A150" s="6">
         <v>149</v>
       </c>
@@ -4175,7 +4965,7 @@
       </c>
       <c r="F150" s="6"/>
     </row>
-    <row r="151" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" ht="15" thickBot="1">
       <c r="A151" s="6">
         <v>150</v>
       </c>
@@ -4495,12 +5285,18 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4A089432-BD68-44B7-B8A9-B3D172848EA8}">
           <x14:formula1>
             <xm:f>Sheet2!$A$1:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>F1:F151</xm:sqref>
+          <xm:sqref>F1</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C1D32574-FBFF-4911-8DD0-B95961D40C27}">
+          <x14:formula1>
+            <xm:f>Sheet2!$A$1:$A$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:F151</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4509,31 +5305,1196 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4889946B-F73F-4F1F-B541-562830883ACD}">
+  <dimension ref="B2:B280"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="18">
+      <c r="B2" s="13" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" s="14"/>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="14" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" s="14" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" s="14" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="14" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="14" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="14" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="14" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="14" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="14" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" s="14" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="14" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" s="14" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2">
+      <c r="B16" s="14" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="14" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="14" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="14" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="14" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="14" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="14" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" ht="18">
+      <c r="B27" s="13" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="14"/>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="14" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="14" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="14" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="14" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="14" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="14" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="14" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="14" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="14" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="14" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="14" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="14" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="14" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="14" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="14" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" ht="18">
+      <c r="B47" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="14"/>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="14" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="14" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="14" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="14" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="14" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" s="14" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" s="14" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="14" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="14" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" s="14" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" s="14" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" s="14" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="14" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" s="14" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="14" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="14" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="14" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="14" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" ht="18">
+      <c r="B70" s="13" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="14"/>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="14" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="14" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="14" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="14" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" s="14" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="14" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" s="14" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="14" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80" s="14" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="14" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" s="14" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="14" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" s="14" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="14" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" s="14" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87" s="14" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" ht="18">
+      <c r="B91" s="13" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92" s="14"/>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93" s="14" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94" s="14" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95" s="14" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96" s="14" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" s="14" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98" s="14" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99" s="14" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100" s="14" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101" s="14" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102" s="14" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103" s="14" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104" s="14" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2">
+      <c r="B105" s="14" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2">
+      <c r="B106" s="14" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107" s="14" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2">
+      <c r="B108" s="14" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109" s="14" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2">
+      <c r="B110" s="14" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2">
+      <c r="B111" s="14" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112" s="14" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" ht="18">
+      <c r="B116" s="13" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117" s="14"/>
+    </row>
+    <row r="118" spans="2:2">
+      <c r="B118" s="14" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2">
+      <c r="B119" s="14" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2">
+      <c r="B120" s="14" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2">
+      <c r="B121" s="14" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2">
+      <c r="B122" s="14" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2">
+      <c r="B123" s="14" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2">
+      <c r="B124" s="14" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2">
+      <c r="B125" s="14" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2">
+      <c r="B126" s="14" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2">
+      <c r="B127" s="14" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2">
+      <c r="B128" s="14" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2">
+      <c r="B129" s="14" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2">
+      <c r="B130" s="14" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2">
+      <c r="B131" s="14" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2">
+      <c r="B132" s="14" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2" ht="18">
+      <c r="B136" s="13" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2">
+      <c r="B137" s="14"/>
+    </row>
+    <row r="138" spans="2:2">
+      <c r="B138" s="14" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2">
+      <c r="B139" s="14" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2">
+      <c r="B140" s="14" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="141" spans="2:2">
+      <c r="B141" s="14" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2">
+      <c r="B142" s="14" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2">
+      <c r="B143" s="14" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2">
+      <c r="B144" s="14" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2">
+      <c r="B145" s="14" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2">
+      <c r="B146" s="14" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2">
+      <c r="B147" s="14" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2">
+      <c r="B148" s="14" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2">
+      <c r="B149" s="14" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2" ht="18">
+      <c r="B153" s="13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2">
+      <c r="B154" s="14"/>
+    </row>
+    <row r="155" spans="2:2">
+      <c r="B155" s="14" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2">
+      <c r="B156" s="14" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2">
+      <c r="B157" s="14" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2">
+      <c r="B158" s="14" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2">
+      <c r="B159" s="14" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2">
+      <c r="B160" s="14" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2">
+      <c r="B161" s="14" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162" s="14" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2">
+      <c r="B163" s="14" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2">
+      <c r="B164" s="14" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2">
+      <c r="B165" s="14" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2">
+      <c r="B166" s="14" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2">
+      <c r="B167" s="14" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2">
+      <c r="B168" s="14" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2">
+      <c r="B169" s="14" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2">
+      <c r="B170" s="14" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2">
+      <c r="B171" s="14" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2">
+      <c r="B172" s="14" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2">
+      <c r="B173" s="14" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2" ht="18">
+      <c r="B177" s="13" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" s="14"/>
+    </row>
+    <row r="179" spans="2:2">
+      <c r="B179" s="14" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2">
+      <c r="B180" s="14" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2">
+      <c r="B181" s="14" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2">
+      <c r="B182" s="14" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2">
+      <c r="B183" s="14" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2">
+      <c r="B184" s="14" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2">
+      <c r="B185" s="14" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="189" spans="2:2" ht="18">
+      <c r="B189" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2">
+      <c r="B190" s="14"/>
+    </row>
+    <row r="191" spans="2:2">
+      <c r="B191" s="14" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2">
+      <c r="B192" s="14" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2">
+      <c r="B193" s="14" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="14" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="14" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="14" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="14" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2">
+      <c r="B198" s="14" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2" ht="18">
+      <c r="B202" s="13" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2">
+      <c r="B203" s="14"/>
+    </row>
+    <row r="204" spans="2:2">
+      <c r="B204" s="14" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2">
+      <c r="B205" s="14" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="206" spans="2:2">
+      <c r="B206" s="14" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2">
+      <c r="B207" s="14" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="208" spans="2:2">
+      <c r="B208" s="14" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2">
+      <c r="B209" s="14" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2">
+      <c r="B210" s="14" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2">
+      <c r="B211" s="14" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="212" spans="2:2">
+      <c r="B212" s="14" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="213" spans="2:2">
+      <c r="B213" s="14" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="214" spans="2:2">
+      <c r="B214" s="14" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="215" spans="2:2">
+      <c r="B215" s="14" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="216" spans="2:2">
+      <c r="B216" s="14" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="220" spans="2:2" ht="18">
+      <c r="B220" s="13" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="221" spans="2:2">
+      <c r="B221" s="14"/>
+    </row>
+    <row r="222" spans="2:2">
+      <c r="B222" s="14" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="223" spans="2:2">
+      <c r="B223" s="14" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2">
+      <c r="B224" s="14" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="225" spans="2:2">
+      <c r="B225" s="14" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="226" spans="2:2">
+      <c r="B226" s="14" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="227" spans="2:2">
+      <c r="B227" s="14" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="228" spans="2:2">
+      <c r="B228" s="14" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="229" spans="2:2">
+      <c r="B229" s="14" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="230" spans="2:2">
+      <c r="B230" s="14" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="234" spans="2:2" ht="18">
+      <c r="B234" s="13" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="235" spans="2:2">
+      <c r="B235" s="14"/>
+    </row>
+    <row r="236" spans="2:2">
+      <c r="B236" s="14" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="237" spans="2:2">
+      <c r="B237" s="14" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="238" spans="2:2">
+      <c r="B238" s="14" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="239" spans="2:2">
+      <c r="B239" s="14" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="240" spans="2:2">
+      <c r="B240" s="14" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="241" spans="2:2">
+      <c r="B241" s="14" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="242" spans="2:2">
+      <c r="B242" s="14" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="243" spans="2:2">
+      <c r="B243" s="14" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="244" spans="2:2">
+      <c r="B244" s="14" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="245" spans="2:2">
+      <c r="B245" s="14" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="249" spans="2:2" ht="18">
+      <c r="B249" s="13" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="250" spans="2:2">
+      <c r="B250" s="14"/>
+    </row>
+    <row r="251" spans="2:2">
+      <c r="B251" s="14" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="252" spans="2:2">
+      <c r="B252" s="14" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="253" spans="2:2">
+      <c r="B253" s="14" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="254" spans="2:2">
+      <c r="B254" s="14" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="255" spans="2:2">
+      <c r="B255" s="14" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="256" spans="2:2">
+      <c r="B256" s="14" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="257" spans="2:2">
+      <c r="B257" s="14" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="258" spans="2:2">
+      <c r="B258" s="14" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="259" spans="2:2">
+      <c r="B259" s="14" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="260" spans="2:2">
+      <c r="B260" s="14" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="264" spans="2:2" ht="18">
+      <c r="B264" s="13" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="265" spans="2:2">
+      <c r="B265" s="14"/>
+    </row>
+    <row r="266" spans="2:2">
+      <c r="B266" s="14" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="267" spans="2:2">
+      <c r="B267" s="14" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="268" spans="2:2">
+      <c r="B268" s="14" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="269" spans="2:2">
+      <c r="B269" s="14" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="270" spans="2:2">
+      <c r="B270" s="14" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="271" spans="2:2">
+      <c r="B271" s="14" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="272" spans="2:2">
+      <c r="B272" s="14" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="273" spans="2:2">
+      <c r="B273" s="14" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="274" spans="2:2">
+      <c r="B274" s="14" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="275" spans="2:2">
+      <c r="B275" s="14" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="276" spans="2:2">
+      <c r="B276" s="14" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="277" spans="2:2">
+      <c r="B277" s="14" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="278" spans="2:2">
+      <c r="B278" s="14" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="279" spans="2:2">
+      <c r="B279" s="14" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="280" spans="2:2">
+      <c r="B280" s="14" t="s">
+        <v>551</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A56F67A8-8B9F-47F1-AE02-7D1177177A32}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>329</v>
       </c>

--- a/dsa-doc/dsa-problems.xlsx
+++ b/dsa-doc/dsa-problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shubh\Projects\DSA\dsa-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF4C5B7-4275-43BF-8B9E-6D127ACC4B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E454DED3-5048-4353-8DD6-1CFBB8C51F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="555">
   <si>
     <t>Num</t>
   </si>
@@ -1778,6 +1778,15 @@
   </si>
   <si>
     <t>207. What is the difference between controlled and uncontrolled components?</t>
+  </si>
+  <si>
+    <t>GitHub: https://github.com/NeoShubh</t>
+  </si>
+  <si>
+    <t>LinkedIn: https://www.linkedin.com/in/shubhamrathore107/</t>
+  </si>
+  <si>
+    <t>✉️ shubhamrathore1024@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -1845,7 +1854,7 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1873,6 +1882,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEA9999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1905,7 +1926,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1949,6 +1970,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2497,7 +2521,9 @@
       <c r="E13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="6"/>
+      <c r="F13" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="14" spans="1:6" ht="15" thickBot="1">
       <c r="A14" s="6">
@@ -2515,7 +2541,9 @@
       <c r="E14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="6"/>
+      <c r="F14" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="15" spans="1:6" ht="15" thickBot="1">
       <c r="A15" s="6">
@@ -5306,141 +5334,153 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4889946B-F73F-4F1F-B541-562830883ACD}">
-  <dimension ref="B2:B280"/>
+  <dimension ref="A2:N280"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="2" spans="2:2" ht="18">
+    <row r="2" spans="1:2" ht="18">
       <c r="B2" s="13" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="3" spans="2:2">
+    <row r="3" spans="1:2">
       <c r="B3" s="14"/>
     </row>
-    <row r="4" spans="2:2">
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>325</v>
+      </c>
       <c r="B4" s="14" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="5" spans="2:2">
+    <row r="5" spans="1:2">
       <c r="B5" s="14" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="6" spans="2:2">
+    <row r="6" spans="1:2">
       <c r="B6" s="14" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="7" spans="2:2">
+    <row r="7" spans="1:2">
       <c r="B7" s="14" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="8" spans="2:2">
+    <row r="8" spans="1:2">
       <c r="B8" s="14" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="9" spans="2:2">
+    <row r="9" spans="1:2">
       <c r="B9" s="14" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="10" spans="2:2">
+    <row r="10" spans="1:2">
       <c r="B10" s="14" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="11" spans="2:2">
+    <row r="11" spans="1:2">
       <c r="B11" s="14" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="12" spans="2:2">
+    <row r="12" spans="1:2">
       <c r="B12" s="14" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="13" spans="2:2">
+    <row r="13" spans="1:2">
       <c r="B13" s="14" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="14" spans="2:2">
+    <row r="14" spans="1:2">
       <c r="B14" s="14" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="15" spans="2:2">
+    <row r="15" spans="1:2">
       <c r="B15" s="14" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="16" spans="2:2">
+    <row r="16" spans="1:2">
       <c r="B16" s="14" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17" spans="2:14">
       <c r="B17" s="14" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18" spans="2:14">
       <c r="B18" s="14" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="2:14">
       <c r="B19" s="14" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="2:14">
       <c r="B20" s="14" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="21" spans="2:2">
+      <c r="N20" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
       <c r="B21" s="14" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="22" spans="2:2">
+      <c r="N21" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
       <c r="B22" s="14" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="23" spans="2:2">
+      <c r="N22" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
       <c r="B23" s="14" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="18">
+    <row r="27" spans="2:14" ht="18">
       <c r="B27" s="13" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="28" spans="2:2">
+    <row r="28" spans="2:14">
       <c r="B28" s="14"/>
     </row>
-    <row r="29" spans="2:2">
+    <row r="29" spans="2:14">
       <c r="B29" s="14" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="30" spans="2:2">
+    <row r="30" spans="2:14">
       <c r="B30" s="14" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="31" spans="2:2">
+    <row r="31" spans="2:14">
       <c r="B31" s="14" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="32" spans="2:2">
+    <row r="32" spans="2:14">
       <c r="B32" s="14" t="s">
         <v>355</v>
       </c>
@@ -6466,12 +6506,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{59E2620A-8BD0-4E4D-A010-EAEC56777DE5}">
+          <x14:formula1>
+            <xm:f>Sheet2!$A$8:$A$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>A308:A455 A1:A307</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A56F67A8-8B9F-47F1-AE02-7D1177177A32}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -6499,6 +6551,21 @@
         <v>329</v>
       </c>
     </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="15" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="16" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="17" t="s">
+        <v>327</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/dsa-doc/dsa-problems.xlsx
+++ b/dsa-doc/dsa-problems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shubh\Projects\DSA\dsa-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E454DED3-5048-4353-8DD6-1CFBB8C51F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E164A6-16DA-4905-BA01-A04761764F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="555">
   <si>
     <t>Num</t>
   </si>
@@ -2561,7 +2561,9 @@
       <c r="E15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="6"/>
+      <c r="F15" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="16" spans="1:6" ht="15" thickBot="1">
       <c r="A16" s="6">
@@ -5354,21 +5356,33 @@
       </c>
     </row>
     <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>325</v>
+      </c>
       <c r="B5" s="14" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>325</v>
+      </c>
       <c r="B6" s="14" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>325</v>
+      </c>
       <c r="B7" s="14" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>325</v>
+      </c>
       <c r="B8" s="14" t="s">
         <v>335</v>
       </c>
@@ -6506,6 +6520,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">

--- a/dsa-doc/dsa-problems.xlsx
+++ b/dsa-doc/dsa-problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shubh\Projects\DSA\dsa-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E164A6-16DA-4905-BA01-A04761764F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD19E76-7BD8-4600-8A86-0166D598A4AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,6 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="555">
   <si>
     <t>Num</t>
   </si>
@@ -2581,7 +2580,9 @@
       <c r="E16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="6"/>
+      <c r="F16" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="17" spans="1:6" ht="15" thickBot="1">
       <c r="A17" s="6">
@@ -2599,7 +2600,9 @@
       <c r="E17" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="6"/>
+      <c r="F17" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="18" spans="1:6" ht="15" thickBot="1">
       <c r="A18" s="6">
@@ -2617,7 +2620,9 @@
       <c r="E18" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="6"/>
+      <c r="F18" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="19" spans="1:6" ht="15" thickBot="1">
       <c r="A19" s="6">
@@ -2635,7 +2640,9 @@
       <c r="E19" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="6"/>
+      <c r="F19" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="15" thickBot="1">
       <c r="A20" s="9">
@@ -2653,7 +2660,9 @@
       <c r="E20" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F20" s="9"/>
+      <c r="F20" s="9" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="21" spans="1:6" ht="15" thickBot="1">
       <c r="A21" s="9">
@@ -2671,7 +2680,9 @@
       <c r="E21" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="9"/>
+      <c r="F21" s="9" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="22" spans="1:6" ht="15" thickBot="1">
       <c r="A22" s="4">
@@ -2689,7 +2700,9 @@
       <c r="E22" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="4"/>
+      <c r="F22" s="4" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="23" spans="1:6" ht="15" thickBot="1">
       <c r="A23" s="6">
@@ -2707,7 +2720,9 @@
       <c r="E23" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F23" s="6"/>
+      <c r="F23" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="24" spans="1:6" ht="15" thickBot="1">
       <c r="A24" s="6">
@@ -2725,7 +2740,9 @@
       <c r="E24" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F24" s="6"/>
+      <c r="F24" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="25" spans="1:6" ht="15" thickBot="1">
       <c r="A25" s="6">
@@ -2743,7 +2760,9 @@
       <c r="E25" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F25" s="6"/>
+      <c r="F25" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="26" spans="1:6" ht="15" thickBot="1">
       <c r="A26" s="6">
@@ -2761,7 +2780,9 @@
       <c r="E26" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F26" s="6"/>
+      <c r="F26" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="27" spans="1:6" ht="15" thickBot="1">
       <c r="A27" s="6">
@@ -2779,7 +2800,9 @@
       <c r="E27" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F27" s="6"/>
+      <c r="F27" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="28" spans="1:6" ht="15" thickBot="1">
       <c r="A28" s="9">
@@ -2797,7 +2820,9 @@
       <c r="E28" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F28" s="9"/>
+      <c r="F28" s="9" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="29" spans="1:6" ht="15" thickBot="1">
       <c r="A29" s="4">
@@ -2815,7 +2840,9 @@
       <c r="E29" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="4"/>
+      <c r="F29" s="4" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="15" thickBot="1">
       <c r="A30" s="6">
@@ -2833,7 +2860,9 @@
       <c r="E30" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F30" s="6"/>
+      <c r="F30" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="15" thickBot="1">
       <c r="A31" s="6">
@@ -2851,7 +2880,9 @@
       <c r="E31" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F31" s="6"/>
+      <c r="F31" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="15" thickBot="1">
       <c r="A32" s="6">
@@ -2869,7 +2900,9 @@
       <c r="E32" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F32" s="6"/>
+      <c r="F32" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="33" spans="1:6" ht="15" thickBot="1">
       <c r="A33" s="6">
@@ -2887,7 +2920,9 @@
       <c r="E33" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F33" s="6"/>
+      <c r="F33" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="34" spans="1:6" ht="15" thickBot="1">
       <c r="A34" s="6">
@@ -2905,7 +2940,9 @@
       <c r="E34" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F34" s="6"/>
+      <c r="F34" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="35" spans="1:6" ht="15" thickBot="1">
       <c r="A35" s="9">
@@ -2923,7 +2960,9 @@
       <c r="E35" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F35" s="9"/>
+      <c r="F35" s="9" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="36" spans="1:6" ht="15" thickBot="1">
       <c r="A36" s="4">
@@ -2941,7 +2980,9 @@
       <c r="E36" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F36" s="4"/>
+      <c r="F36" s="4" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="37" spans="1:6" ht="15" thickBot="1">
       <c r="A37" s="4">
@@ -2959,7 +3000,9 @@
       <c r="E37" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F37" s="4"/>
+      <c r="F37" s="4" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1">
       <c r="A38" s="6">
@@ -2977,7 +3020,9 @@
       <c r="E38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F38" s="6"/>
+      <c r="F38" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="39" spans="1:6" ht="15" thickBot="1">
       <c r="A39" s="6">
@@ -2995,7 +3040,9 @@
       <c r="E39" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F39" s="6"/>
+      <c r="F39" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="40" spans="1:6" ht="15" thickBot="1">
       <c r="A40" s="6">
@@ -3013,7 +3060,9 @@
       <c r="E40" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F40" s="6"/>
+      <c r="F40" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="41" spans="1:6" ht="15" thickBot="1">
       <c r="A41" s="6">
@@ -3031,7 +3080,9 @@
       <c r="E41" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F41" s="6"/>
+      <c r="F41" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="42" spans="1:6" ht="15" thickBot="1">
       <c r="A42" s="4">
@@ -3049,7 +3100,9 @@
       <c r="E42" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F42" s="4"/>
+      <c r="F42" s="4" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1">
       <c r="A43" s="6">
@@ -3067,7 +3120,9 @@
       <c r="E43" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F43" s="6"/>
+      <c r="F43" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="44" spans="1:6" ht="15" thickBot="1">
       <c r="A44" s="6">
@@ -3085,7 +3140,9 @@
       <c r="E44" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F44" s="6"/>
+      <c r="F44" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="45" spans="1:6" ht="15" thickBot="1">
       <c r="A45" s="9">
@@ -3103,7 +3160,9 @@
       <c r="E45" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F45" s="9"/>
+      <c r="F45" s="9" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="46" spans="1:6" ht="15" thickBot="1">
       <c r="A46" s="9">
@@ -3121,7 +3180,9 @@
       <c r="E46" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F46" s="9"/>
+      <c r="F46" s="9" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="47" spans="1:6" ht="15" thickBot="1">
       <c r="A47" s="4">
@@ -3139,7 +3200,9 @@
       <c r="E47" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="4"/>
+      <c r="F47" s="4" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="48" spans="1:6" ht="15" thickBot="1">
       <c r="A48" s="4">
@@ -3157,7 +3220,9 @@
       <c r="E48" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F48" s="4"/>
+      <c r="F48" s="4" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="49" spans="1:6" ht="15" thickBot="1">
       <c r="A49" s="4">
@@ -3175,7 +3240,9 @@
       <c r="E49" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="4"/>
+      <c r="F49" s="4" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="50" spans="1:6" ht="15" thickBot="1">
       <c r="A50" s="4">
@@ -3193,7 +3260,9 @@
       <c r="E50" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F50" s="4"/>
+      <c r="F50" s="4" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="51" spans="1:6" ht="15" thickBot="1">
       <c r="A51" s="4">
@@ -3211,7 +3280,9 @@
       <c r="E51" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F51" s="4"/>
+      <c r="F51" s="4" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="52" spans="1:6" ht="15" thickBot="1">
       <c r="A52" s="4">
@@ -3229,7 +3300,9 @@
       <c r="E52" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="4"/>
+      <c r="F52" s="4" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="53" spans="1:6" ht="15" thickBot="1">
       <c r="A53" s="6">
